--- a/output/2026-10-05_21_Croazia_Međimurska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-05_21_Croazia_Međimurska_Depolverazione_Trattamento_aria.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,6 @@
           <t>+385 1 3818 004</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Filtration Group Industrial Premium Partner, distributore soluzioni filtrazione aria industriale. Email non verificabile da fonte diretta, lasciata vuota. Contatto: Jozo Semren. Fonte: pagina ufficiale partner Filtration Group.</t>
@@ -590,7 +589,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
@@ -620,7 +619,6 @@
           <t>+385 1 2456 180</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Distributore attrezzature saldatura/taglio/automazione, include linee aspirazione fumi di saldatura e polveri di smerigliatura (settore adiacente trattamento aria). Email non verificabile da fonte diretta, lasciata vuota. Fonte: sito ufficiale (WebFetch diretto).</t>
